--- a/recommendations_results.xlsx
+++ b/recommendations_results.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Query1_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Query2_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Query3_Results" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +470,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -481,34 +483,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MATHDEAN762</t>
+          <t>GEOG484</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Machine Learning in Geospatial Science</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Visualization methods applied to data. Both human perception and statistical
-properties inform the methods used to display and visually explore categorical, continuous, time-ordered, map, and high dimensional data. Order and layout effects on tables and graphics. Statistical concepts visually presented include variability, densities, quantiles, conditioning, and hypothesis testing. Interactive graphics
-include linking, brushing, motion, and the navigation of high dimensional spaces guided via projection indices. Glyphs (e.g. cartoon, statistical, or heatmap) and radial and parallel coordinates.</t>
+          <t>An in-depth study of current machine learning algorithms and their applications in geospatial science, with a focus on earth observation data processing and analysis. Topics include k-nearest neighbour, decision trees, support vector machines, ensemble learning, and some deep neural networks (e.g., CNN, U-Net). Machine learning algorithms implemented using Python will be applied for semantic segmentation, land use and land cover classification, and building and road detection using aerial and satellite images.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.448587822405437</v>
+        <v>0.806925682183252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -516,34 +516,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>STATACTSC842</t>
+          <t>CS485</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Statistical and Computational Foundations of Machine Learning</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Visualization methods applied to data. Both human perception and statistical
-properties inform the methods used to display and visually explore categorical, continuous, time-ordered, map, and high dimensional data. Order and layout effects on tables and graphics. Statistical concepts visually presented include variability, densities, quantiles, conditioning, and hypothesis testing. Interactive graphics
-include linking, brushing, motion, and the navigation of high dimensional spaces guided via projection indices. Glyphs (e.g. cartoon, statistical, or heatmap) and radial and parallel coordinates.</t>
+          <t>Extracting meaningful patterns from random samples of large data sets. Statistical analysis of the resulting problems. Common algorithmic paradigms for such tasks. Central concepts: VC-dimension, margins of a classifier, sparsity and description length, other types of regularization. Performance guarantees: generalization bounds, data dependent error bounds, and computational complexity of learning algorithms. Common paradigms: neural networks, kernel methods and support-vector machines, boosting, nearest neighbor classifiers. Applications to data mining.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.447668282175552</v>
+        <v>0.7523133020917343</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -551,225 +549,225 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>STATACTSC442</t>
+          <t>CS480</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Visualization methods applied to data. Both human perception and statistical properties inform the methods used to display and visually explore categorical, continuous, time-ordered, map, and high dimensional data. Order and layout effects on tables and graphics. Statistical concepts visually presented include variability, densities, quantiles, conditioning, and hypothesis testing. Interactive graphics include linking, brushing, motion, and the navigation of high dimensional spaces guided via projection indices. Glyphs (e.g., cartoon, statistical, or heatmap) and radial and parallel coordinates.</t>
+          <t>Introduction to modelling and algorithmic techniques for machines to learn concepts from data. Generalization: underfitting, overfitting, cross-validation. Tasks: classification, regression, clustering. Optimization-based learning: loss minimization. regularization. Statistical learning: maximum likelihood, Bayesian learning. Algorithms: nearest neighbour, (generalized) linear regression, mixtures of Gaussians, Gaussian processes, kernel methods, support vector machines, deep learning, sequence learning, ensemble techniques. Large scale learning: distributed learning and stream learning. Applications: Natural language processing, computer vision, data mining, human computer interaction, information retrieval.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.4476344086021506</v>
+        <v>0.7053827754993268</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FINE209</t>
+          <t>SYDE522</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Global Modernisms: 1940-1970</t>
+          <t>Foundations of Artificial Intelligence</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>This course introduces students to a thematically, materially, and geographically varied set of art practices which developed across the world from 1940-1970 and are referred to, under different monikers, as high modernism, mid-century modernism, and more recently global modernism. These variants of global art production are explored by analyzing theoretical and aesthetic ideas, as well as art movements and styles such as Socialist Realism, Gutai, Postcolonial Modernism, Cannibalist Aesthetic, Brutalism, Abstract Expressionism, Pop Art, Négritude, Indigenous Modernism, and others.</t>
+          <t>The objective of this course is to introduce students to fundamental concepts of artificial intelligence. An overview of different learning schemes will be provided, including supervised and unsupervised algorithms. The focus of this course will be on dimensionality reduction, clustering, classification, deep and shallow artificial neural networks, and reinforcement learning. Ethical aspects of artificial intelligence will be discussed.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6985055804252625</v>
+        <v>0.6577969732328739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>REN301</t>
+          <t>AMATH445</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Language, Culture, and Identity</t>
+          <t>Scientific Machine Learning</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>This course provides an introductory overview of fundamental concepts of language, culture, and identity and relates them to foreign/second language learning and teaching. The course is not language-specific but rather addresses general questions related to learning and using more than one language.</t>
+          <t>The course provides an in-depth exploration of how deep learning techniques are applied in various scientific and medical domains. The course introduces basic concepts of deep learning, explores different deep learning architectures and algorithms, and focuses on their applications in scientific and biomedical research. The integration of scientific knowledge with machine learning techniques is emphasized throughout the course. Students will gain hands-on experience by executing the acquired concepts using Python.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.6985055804252625</v>
+        <v>0.6528561504203062</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BIOL266</t>
+          <t>CS240</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Introduction to Computational Biology</t>
+          <t>Data Structures and Data Management</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>This course provides an introduction to computational methods in biology, including exploration of bioinformatics databases and tools, analysis of protein and DNA sequences, and computer-aided modelling of biological systems. Labs will include practical experience applying computational tools to biological problems.</t>
+          <t>Introduction to widely used and effective methods of data organization, focusing on data structures, their algorithms, and the performance of these algorithms. Specific topics include priority queues, sorting, dictionaries, data structures for text processing.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.6969822645187378</v>
+        <v>0.6201455930649373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SYDE760</t>
+          <t>MSE240</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Topics in Engineering Design</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Topics in Engineering Design</t>
+          <t>Design and analysis of data structures and algorithms with an emphasis on further development of computer programming skills. Topics include algorithms for searching, sorting, stacks, queues, trees, and graphs. Comparison of algorithms on different data structures. Solutions to common engineering problems in computer science using algorithms and data structures. Introduction to mathematical analysis of space and time complexity with a focus on designing solutions that can scale to large input sizes.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.549209486166008</v>
+        <v>0.6096059347321132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CS846</t>
+          <t>ECE250</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Advanced Topics in Software Engineering</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Advanced Topics in Software Engineering</t>
+          <t>Data structures, abstract data types, recursive algorithms, algorithm analysis, sorting and searching, and problem-solving strategies.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.5236363636363637</v>
+        <v>0.6059140051353811</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>cosine</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ME760</t>
+          <t>ECE457B</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Special Topics in Thermal Engineering</t>
+          <t>Fundamentals of Computational Intelligence</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Special Topics in Thermal Engineering</t>
+          <t>Fundamentals and recent advances in computational intelligence. Building accurate models with collected data or rules bases. Model-based prediction and classification. Concepts in machine learning, supervised and unsupervised learning, artificial neural networks, deep learning, feature extraction, feature selection, dimensionality reduction, classification and clustering, support vector machines. Approximate reasoning based on fuzzy set theory. Performance metrics to assess the validity of produced models. Multiple examples and case studies such as autonomous driving, intelligent manufacturing, natural language understanding, speech recognition, computer vision, stock market prediction, disease early detection and diagnosis.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.5189577717879604</v>
+        <v>0.6046502716172735</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -778,97 +776,97 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CIVE497</t>
+          <t>MSE446</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Special Topics in Geological Engineering</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A special topics course on advanced topics in geological engineering is offered from time to time, when resources are available. For the current offering, inquire at the Department.</t>
+          <t>This course provides an introduction to machine learning, including supervised and unsupervised learning. Emphasis is placed on proper procedures for the training and testing of models. Topics covered may include data cleaning and transformation, overfitting and generalization, n-fold cross validation, regression, decision trees, neural networks, rule finding, and clustering. Students learn to apply machine learning methods to management engineering problems using common tools such as R and Python.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8943619800000286</v>
+        <v>0.6035082944708232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>faiss</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GEOG407</t>
+          <t>GEOG484</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Environmental Hydrology of Terrestrial Ecosystems</t>
+          <t>Machine Learning in Geospatial Science</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>This course focuses on ecological and biogeochemical processes that are linked to the terrestrial hydrological cycle and how these relate to the management of natural resources. The objectives of this interdisciplinary course are to explore topics that integrate ecosystem processes with physical hydrology and examine the impacts of human activities on ecohydrological and hydrochemical processes within terrestrial systems. This course focuses on the storage and movement of water, solutes, and nutrients within selected ecosystems (forests, agricultural, wetlands), considering the biogeochemical consequences of human activity such as climate change, wetland drainage, agriculture, and forest harvesting.</t>
+          <t>An in-depth study of current machine learning algorithms and their applications in geospatial science, with a focus on earth observation data processing and analysis. Topics include k-nearest neighbour, decision trees, support vector machines, ensemble learning, and some deep neural networks (e.g., CNN, U-Net). Machine learning algorithms implemented using Python will be applied for semantic segmentation, land use and land cover classification, and building and road detection using aerial and satellite images.</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8885825140501689</v>
+        <v>0.8069257140159607</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>faiss</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SYDE662</t>
+          <t>CS485</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Systems Design Graduate Workshop 2</t>
+          <t>Statistical and Computational Foundations of Machine Learning</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>This course builds upon SYDE660, SYDE660A, SYDE660B, SYDE660C, SYDE660D, or SYDE660E. The project undertaken in this course can either be a continuation of the project in one of these courses or a new project. Expectations in this course are that the design undertaken also includes prototype testing, evaluation, and final design specification.</t>
+          <t>Extracting meaningful patterns from random samples of large data sets. Statistical analysis of the resulting problems. Common algorithmic paradigms for such tasks. Central concepts: VC-dimension, margins of a classifier, sparsity and description length, other types of regularization. Performance guarantees: generalization bounds, data dependent error bounds, and computational complexity of learning algorithms. Common paradigms: neural networks, kernel methods and support-vector machines, boosting, nearest neighbor classifiers. Applications to data mining.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8844350002615824</v>
+        <v>0.7523132562637329</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -877,31 +875,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIVE497</t>
+          <t>CS480</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Special Topics in Geological Engineering</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A special topics course on advanced topics in geological engineering is offered from time to time, when resources are available. For the current offering, inquire at the Department.</t>
+          <t>Introduction to modelling and algorithmic techniques for machines to learn concepts from data. Generalization: underfitting, overfitting, cross-validation. Tasks: classification, regression, clustering. Optimization-based learning: loss minimization. regularization. Statistical learning: maximum likelihood, Bayesian learning. Algorithms: nearest neighbour, (generalized) linear regression, mixtures of Gaussians, Gaussian processes, kernel methods, support vector machines, deep learning, sequence learning, ensemble techniques. Large scale learning: distributed learning and stream learning. Applications: Natural language processing, computer vision, data mining, human computer interaction, information retrieval.</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8943620324134827</v>
+        <v>0.7053828835487366</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -910,31 +908,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GEOG407</t>
+          <t>SYDE522</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Environmental Hydrology of Terrestrial Ecosystems</t>
+          <t>Foundations of Artificial Intelligence</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>This course focuses on ecological and biogeochemical processes that are linked to the terrestrial hydrological cycle and how these relate to the management of natural resources. The objectives of this interdisciplinary course are to explore topics that integrate ecosystem processes with physical hydrology and examine the impacts of human activities on ecohydrological and hydrochemical processes within terrestrial systems. This course focuses on the storage and movement of water, solutes, and nutrients within selected ecosystems (forests, agricultural, wetlands), considering the biogeochemical consequences of human activity such as climate change, wetland drainage, agriculture, and forest harvesting.</t>
+          <t>The objective of this course is to introduce students to fundamental concepts of artificial intelligence. An overview of different learning schemes will be provided, including supervised and unsupervised algorithms. The focus of this course will be on dimensionality reduction, clustering, classification, deep and shallow artificial neural networks, and reinforcement learning. Ethical aspects of artificial intelligence will be discussed.</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8885824680328369</v>
+        <v>0.6577970385551453</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -943,531 +941,531 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SYDE662</t>
+          <t>AMATH445</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Systems Design Graduate Workshop 2</t>
+          <t>Scientific Machine Learning</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>This course builds upon SYDE660, SYDE660A, SYDE660B, SYDE660C, SYDE660D, or SYDE660E. The project undertaken in this course can either be a continuation of the project in one of these courses or a new project. Expectations in this course are that the design undertaken also includes prototype testing, evaluation, and final design specification.</t>
+          <t>The course provides an in-depth exploration of how deep learning techniques are applied in various scientific and medical domains. The course introduces basic concepts of deep learning, explores different deep learning architectures and algorithms, and focuses on their applications in scientific and biomedical research. The integration of scientific knowledge with machine learning techniques is emphasized throughout the course. Students will gain hands-on experience by executing the acquired concepts using Python.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8844351172447205</v>
+        <v>0.6528562307357788</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>faiss</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ENGL780</t>
+          <t>CS240</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Studies in Genre</t>
+          <t>Data Structures and Data Management</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Studies in Genre</t>
+          <t>Introduction to widely used and effective methods of data organization, focusing on data structures, their algorithms, and the performance of these algorithms. Specific topics include priority queues, sorting, dictionaries, data structures for text processing.</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.5494208494208495</v>
+        <v>0.6201455593109131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>faiss</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STATACTSC992</t>
+          <t>MSE240</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seminar in Actuarial Science</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Seminar in Actuarial Science</t>
+          <t>Design and analysis of data structures and algorithms with an emphasis on further development of computer programming skills. Topics include algorithms for searching, sorting, stacks, queues, trees, and graphs. Comparison of algorithms on different data structures. Solutions to common engineering problems in computer science using algorithms and data structures. Introduction to mathematical analysis of space and time complexity with a focus on designing solutions that can scale to large input sizes.</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.4957328385899815</v>
+        <v>0.6096059679985046</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>faiss</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CS886</t>
+          <t>ECE250</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Advanced Topics in Artificial Intelligence</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Advanced Topics in Artificial Intelligence</t>
+          <t>Data structures, abstract data types, recursive algorithms, algorithm analysis, sorting and searching, and problem-solving strategies.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.4648351648351648</v>
+        <v>0.6059141159057617</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>faiss</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SYDE660E</t>
+          <t>ECE457B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Systems Design Graduate Workshop 1 - Vision, Image &amp; Signal Processing</t>
+          <t>Fundamentals of Computational Intelligence</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Engineering design project course where students work in small groups applying the principles of engineering problem solving, research methods, systems analysis including modelling, simulation, optimization and design. There is a strong focus on a major vision, image and signal processing design project with regular mentorship, project update reports and presentations, project reviews, and design embodiment demonstrations.</t>
+          <t>Fundamentals and recent advances in computational intelligence. Building accurate models with collected data or rules bases. Model-based prediction and classification. Concepts in machine learning, supervised and unsupervised learning, artificial neural networks, deep learning, feature extraction, feature selection, dimensionality reduction, classification and clustering, support vector machines. Approximate reasoning based on fuzzy set theory. Performance metrics to assess the validity of produced models. Multiple examples and case studies such as autonomous driving, intelligent manufacturing, natural language understanding, speech recognition, computer vision, stock market prediction, disease early detection and diagnosis.</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.5469037890434265</v>
+        <v>0.6046503186225891</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>faiss</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ME421</t>
+          <t>MSE446</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Linear and Nonlinear Electronics</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The performance of single, differential, and multistage amplifiers. The cascode configuration, current mirror, and active loads. A detailed study of operational amplifier circuits. Transistor frequency response analysis. Feedback circuit configurations and oscillators. A detailed study of stability and compensation for multistage and operational amplifiers. Introduction to common circuit blocks; A/D (analog-to-digital) converters, D/A (digital-to-analog) converters, and phase-locked loops.</t>
+          <t>This course provides an introduction to machine learning, including supervised and unsupervised learning. Emphasis is placed on proper procedures for the training and testing of models. Topics covered may include data cleaning and transformation, overfitting and generalization, n-fold cross validation, regression, decision trees, neural networks, rule finding, and clustering. Students learn to apply machine learning methods to management engineering problems using common tools such as R and Python.</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.5033066868782043</v>
+        <v>0.6035083532333374</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business Intelligence</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ENGDEAN495</t>
+          <t>GEOG484</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Design Intensive Special Topics in Environmental Engineering</t>
+          <t>Machine Learning in Geospatial Science</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A special topics course on design intensive advanced topics in environmental engineering is offered from time to time, when resources are available. For the current offering, inquire at the Department.</t>
+          <t>An in-depth study of current machine learning algorithms and their applications in geospatial science, with a focus on earth observation data processing and analysis. Topics include k-nearest neighbour, decision trees, support vector machines, ensemble learning, and some deep neural networks (e.g., CNN, U-Net). Machine learning algorithms implemented using Python will be applied for semantic segmentation, land use and land cover classification, and building and road detection using aerial and satellite images.</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.4833661913871765</v>
+        <v>0.806925682183252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GEOG407</t>
+          <t>CS485</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Environmental Hydrology of Terrestrial Ecosystems</t>
+          <t>Statistical and Computational Foundations of Machine Learning</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>This course focuses on ecological and biogeochemical processes that are linked to the terrestrial hydrological cycle and how these relate to the management of natural resources. The objectives of this interdisciplinary course are to explore topics that integrate ecosystem processes with physical hydrology and examine the impacts of human activities on ecohydrological and hydrochemical processes within terrestrial systems. This course focuses on the storage and movement of water, solutes, and nutrients within selected ecosystems (forests, agricultural, wetlands), considering the biogeochemical consequences of human activity such as climate change, wetland drainage, agriculture, and forest harvesting.</t>
+          <t>Extracting meaningful patterns from random samples of large data sets. Statistical analysis of the resulting problems. Common algorithmic paradigms for such tasks. Central concepts: VC-dimension, margins of a classifier, sparsity and description length, other types of regularization. Performance guarantees: generalization bounds, data dependent error bounds, and computational complexity of learning algorithms. Common paradigms: neural networks, kernel methods and support-vector machines, boosting, nearest neighbor classifiers. Applications to data mining.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.9245272034096166</v>
+        <v>0.7523133020917343</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CIVE497</t>
+          <t>AMATH445</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Special Topics in Geological Engineering</t>
+          <t>Scientific Machine Learning</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>A special topics course on advanced topics in geological engineering is offered from time to time, when resources are available. For the current offering, inquire at the Department.</t>
+          <t>The course provides an in-depth exploration of how deep learning techniques are applied in various scientific and medical domains. The course introduces basic concepts of deep learning, explores different deep learning architectures and algorithms, and focuses on their applications in scientific and biomedical research. The integration of scientific knowledge with machine learning techniques is emphasized throughout the course. Students will gain hands-on experience by executing the acquired concepts using Python.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.9105052307993704</v>
+        <v>0.6528561504203062</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SYDE662</t>
+          <t>CS480</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Systems Design Graduate Workshop 2</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>This course builds upon SYDE660, SYDE660A, SYDE660B, SYDE660C, SYDE660D, or SYDE660E. The project undertaken in this course can either be a continuation of the project in one of these courses or a new project. Expectations in this course are that the design undertaken also includes prototype testing, evaluation, and final design specification.</t>
+          <t>Introduction to modelling and algorithmic techniques for machines to learn concepts from data. Generalization: underfitting, overfitting, cross-validation. Tasks: classification, regression, clustering. Optimization-based learning: loss minimization. regularization. Statistical learning: maximum likelihood, Bayesian learning. Algorithms: nearest neighbour, (generalized) linear regression, mixtures of Gaussians, Gaussian processes, kernel methods, support vector machines, deep learning, sequence learning, ensemble techniques. Large scale learning: distributed learning and stream learning. Applications: Natural language processing, computer vision, data mining, human computer interaction, information retrieval.</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.9078902312944427</v>
+        <v>0.7053827754993268</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GEOG407</t>
+          <t>MSE240</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Environmental Hydrology of Terrestrial Ecosystems</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>This course focuses on ecological and biogeochemical processes that are linked to the terrestrial hydrological cycle and how these relate to the management of natural resources. The objectives of this interdisciplinary course are to explore topics that integrate ecosystem processes with physical hydrology and examine the impacts of human activities on ecohydrological and hydrochemical processes within terrestrial systems. This course focuses on the storage and movement of water, solutes, and nutrients within selected ecosystems (forests, agricultural, wetlands), considering the biogeochemical consequences of human activity such as climate change, wetland drainage, agriculture, and forest harvesting.</t>
+          <t>Design and analysis of data structures and algorithms with an emphasis on further development of computer programming skills. Topics include algorithms for searching, sorting, stacks, queues, trees, and graphs. Comparison of algorithms on different data structures. Solutions to common engineering problems in computer science using algorithms and data structures. Introduction to mathematical analysis of space and time complexity with a focus on designing solutions that can scale to large input sizes.</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.9245272278785706</v>
+        <v>0.6096059347321132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CIVE497</t>
+          <t>SYDE522</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Special Topics in Geological Engineering</t>
+          <t>Foundations of Artificial Intelligence</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A special topics course on advanced topics in geological engineering is offered from time to time, when resources are available. For the current offering, inquire at the Department.</t>
+          <t>The objective of this course is to introduce students to fundamental concepts of artificial intelligence. An overview of different learning schemes will be provided, including supervised and unsupervised algorithms. The focus of this course will be on dimensionality reduction, clustering, classification, deep and shallow artificial neural networks, and reinforcement learning. Ethical aspects of artificial intelligence will be discussed.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.9105052351951599</v>
+        <v>0.6577969732328739</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SYDE662</t>
+          <t>ENGL208B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Systems Design Graduate Workshop 2</t>
+          <t>Science Fiction</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>This course builds upon SYDE660, SYDE660A, SYDE660B, SYDE660C, SYDE660D, or SYDE660E. The project undertaken in this course can either be a continuation of the project in one of these courses or a new project. Expectations in this course are that the design undertaken also includes prototype testing, evaluation, and final design specification.</t>
+          <t>Various examples drawn, for instance, from Utopian and anti-Utopian science fiction, social science fiction, "gadget" science fiction, parapsychology, and alternate worlds and beings will be considered. Some attention will be given to the historical development of the genre.</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.9078902006149292</v>
+        <v>0.3561408209037448</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CO779</t>
+          <t>CS448</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Topics in Operations Research</t>
+          <t>Database Systems Implementation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Topics in Operations Research</t>
+          <t>The objective of this course is to introduce students to fundamentals of building a relational database management system. The course focuses on the database engine core technology by studying topics such as storage management (data layout, disk-based data structures), indexing, query processing algorithms, query optimization, transactional concurrency control, logging and recovery.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5346215231704312</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CO879</t>
+          <t>CS240</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Seminar in Operations Research</t>
+          <t>Data Structures and Data Management</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seminar in Operations Research</t>
+          <t>Introduction to widely used and effective methods of data organization, focusing on data structures, their algorithms, and the performance of these algorithms. Specific topics include priority queues, sorting, dictionaries, data structures for text processing.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5226190476190475</v>
+        <v>0.6201455930649373</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>mmr</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENGL725</t>
+          <t>MATH199</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Studies in Romanticism</t>
+          <t>Mathematical Discovery and Invention</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Studies in Romanticism</t>
+          <t>A course in problem solving in which intriguing and difficult problems are solved. Problems are taken mainly from the elementary parts of applied mathematics, computer science, statistics and actuarial science, pure mathematics, and combinatorics and optimization. Material relevant to the problems is taught in depth.</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.4467166979362102</v>
+        <v>0.464561808504573</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1475,32 +1473,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ENGL710</t>
+          <t>AMATH445</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Studies in Renaissance Drama</t>
+          <t>Scientific Machine Learning</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Studies in Renaissance Drama</t>
+          <t>The course provides an in-depth exploration of how deep learning techniques are applied in various scientific and medical domains. The course introduces basic concepts of deep learning, explores different deep learning architectures and algorithms, and focuses on their applications in scientific and biomedical research. The integration of scientific knowledge with machine learning techniques is emphasized throughout the course. Students will gain hands-on experience by executing the acquired concepts using Python.</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.6957489252090454</v>
+        <v>0.002176980381630106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1508,32 +1506,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ENGL730</t>
+          <t>CS240</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Studies in Victorian Literature</t>
+          <t>Data Structures and Data Management</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Studies in Victorian Literature</t>
+          <t>Introduction to widely used and effective methods of data organization, focusing on data structures, their algorithms, and the performance of these algorithms. Specific topics include priority queues, sorting, dictionaries, data structures for text processing.</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.6522859930992126</v>
+        <v>0.002029643293867964</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1541,258 +1539,258 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ENGL705</t>
+          <t>CS480</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Studies in Old and Middle English Literature</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Studies in Old and Middle English Literature</t>
+          <t>Introduction to modelling and algorithmic techniques for machines to learn concepts from data. Generalization: underfitting, overfitting, cross-validation. Tasks: classification, regression, clustering. Optimization-based learning: loss minimization. regularization. Statistical learning: maximum likelihood, Bayesian learning. Algorithms: nearest neighbour, (generalized) linear regression, mixtures of Gaussians, Gaussian processes, kernel methods, support vector machines, deep learning, sequence learning, ensemble techniques. Large scale learning: distributed learning and stream learning. Applications: Natural language processing, computer vision, data mining, human computer interaction, information retrieval.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.604196310043335</v>
+        <v>0.001903030846219979</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ARTSDEAN653</t>
+          <t>CS485</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>International Organizations and Public Policy</t>
+          <t>Statistical and Computational Foundations of Machine Learning</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>This course explores international organizations' contributions to transnational or "multilevel" governance and the instruments (both hard and soft) that they can wield.  Students assess the role of international organizations in transnational policy diffusion by focusing first on major international organizations such as the International Monetary Fund, the World Bank and the OECD and then examine key policy areas such as the environment, food and development.</t>
+          <t>Extracting meaningful patterns from random samples of large data sets. Statistical analysis of the resulting problems. Common algorithmic paradigms for such tasks. Central concepts: VC-dimension, margins of a classifier, sparsity and description length, other types of regularization. Performance guarantees: generalization bounds, data dependent error bounds, and computational complexity of learning algorithms. Common paradigms: neural networks, kernel methods and support-vector machines, boosting, nearest neighbor classifiers. Applications to data mining.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.9110810712684805</v>
+        <v>0.001774650550158623</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SEED642</t>
+          <t>ECE250</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stakeholder Engagement, Collaborations and Partnerships</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>This course builds competences in the development and deployment of strategies and processes (in for-and not-for-profit organizations) to engage both internal and external stakeholders in opportunities to accelerate sustainability.  Content covers: the identification, characterization and valuation of primary and secondary stakeholders; drivers and challenges; engagement approaches, including traditional and social media forms of communication, consultation, conflict resolution, and cross-sector partnerships.  Content also introduces: structures, including informal vs. formal interactions, face-to-face and distance meetings, industry associations, joint ventures, public-private partnerships, networks and business to not-for-profit collaborations; processes, such as partnership formation, decision-making, monitoring of progress; and strategic considerations, such as business value, risk management, control vs. influence, barriers and confluence points.  Students working as a team will present their recommendations on a real time case study to stakeholders involved.</t>
+          <t>Data structures, abstract data types, recursive algorithms, algorithm analysis, sorting and searching, and problem-solving strategies.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.821237377822078</v>
+        <v>0.001761320853794309</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEED606</t>
+          <t>ECE457B</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Energy Sustainability</t>
+          <t>Fundamentals of Computational Intelligence</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Renewable and non-renewable energy supply systems are compared using economic and environmental measures. Consumption trends, conservation options and choices are considered at the household, community and global scales. Projects are used to demonstrate the economic and environmental challenges in the design of sustainable energy systems. *eligible for MES.</t>
+          <t>Fundamentals and recent advances in computational intelligence. Building accurate models with collected data or rules bases. Model-based prediction and classification. Concepts in machine learning, supervised and unsupervised learning, artificial neural networks, deep learning, feature extraction, feature selection, dimensionality reduction, classification and clustering, support vector machines. Approximate reasoning based on fuzzy set theory. Performance metrics to assess the validity of produced models. Multiple examples and case studies such as autonomous driving, intelligent manufacturing, natural language understanding, speech recognition, computer vision, stock market prediction, disease early detection and diagnosis.</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7900513000480246</v>
+        <v>0.001673072030876497</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ARTSDEAN653</t>
+          <t>GEOG484</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>International Organizations and Public Policy</t>
+          <t>Machine Learning in Geospatial Science</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>This course explores international organizations' contributions to transnational or "multilevel" governance and the instruments (both hard and soft) that they can wield.  Students assess the role of international organizations in transnational policy diffusion by focusing first on major international organizations such as the International Monetary Fund, the World Bank and the OECD and then examine key policy areas such as the environment, food and development.</t>
+          <t>An in-depth study of current machine learning algorithms and their applications in geospatial science, with a focus on earth observation data processing and analysis. Topics include k-nearest neighbour, decision trees, support vector machines, ensemble learning, and some deep neural networks (e.g., CNN, U-Net). Machine learning algorithms implemented using Python will be applied for semantic segmentation, land use and land cover classification, and building and road detection using aerial and satellite images.</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.9110811352729797</v>
+        <v>0.001644637405574247</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SEED642</t>
+          <t>MSE240</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stakeholder Engagement, Collaborations and Partnerships</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>This course builds competences in the development and deployment of strategies and processes (in for-and not-for-profit organizations) to engage both internal and external stakeholders in opportunities to accelerate sustainability.  Content covers: the identification, characterization and valuation of primary and secondary stakeholders; drivers and challenges; engagement approaches, including traditional and social media forms of communication, consultation, conflict resolution, and cross-sector partnerships.  Content also introduces: structures, including informal vs. formal interactions, face-to-face and distance meetings, industry associations, joint ventures, public-private partnerships, networks and business to not-for-profit collaborations; processes, such as partnership formation, decision-making, monitoring of progress; and strategic considerations, such as business value, risk management, control vs. influence, barriers and confluence points.  Students working as a team will present their recommendations on a real time case study to stakeholders involved.</t>
+          <t>Design and analysis of data structures and algorithms with an emphasis on further development of computer programming skills. Topics include algorithms for searching, sorting, stacks, queues, trees, and graphs. Comparison of algorithms on different data structures. Solutions to common engineering problems in computer science using algorithms and data structures. Introduction to mathematical analysis of space and time complexity with a focus on designing solutions that can scale to large input sizes.</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8212373852729797</v>
+        <v>0.001634677060427345</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SEED606</t>
+          <t>MSE446</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Energy Sustainability</t>
+          <t>Introduction to Machine Learning</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Renewable and non-renewable energy supply systems are compared using economic and environmental measures. Consumption trends, conservation options and choices are considered at the household, community and global scales. Projects are used to demonstrate the economic and environmental challenges in the design of sustainable energy systems. *eligible for MES.</t>
+          <t>This course provides an introduction to machine learning, including supervised and unsupervised learning. Emphasis is placed on proper procedures for the training and testing of models. Topics covered may include data cleaning and transformation, overfitting and generalization, n-fold cross validation, regression, decision trees, neural networks, rule finding, and clustering. Students learn to apply machine learning methods to management engineering problems using common tools such as R and Python.</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.7900513410568237</v>
+        <v>0.001631267672007478</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ENGL791</t>
+          <t>SYDE522</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Professional Writing</t>
+          <t>Foundations of Artificial Intelligence</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Professional Writing</t>
+          <t>The objective of this course is to introduce students to fundamental concepts of artificial intelligence. An overview of different learning schemes will be provided, including supervised and unsupervised algorithms. The focus of this course will be on dimensionality reduction, clustering, classification, deep and shallow artificial neural networks, and reinforcement learning. Ethical aspects of artificial intelligence will be discussed.</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.4423157894736842</v>
+        <v>0.001628186766418545</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,31 +1799,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ME749</t>
+          <t>PHYS449</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Special Topics in Machining</t>
+          <t>Machine Learning in Physics</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Special Topics in Machining</t>
+          <t>Machine learning applications in the physical sciences.</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.44</v>
+        <v>0.5777961888980945</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1834,522 +1832,6661 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CO765</t>
+          <t>CS399</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mathematical Programming</t>
+          <t>Readings in Computer Science</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mathematical Programming</t>
+          <t>Reading course as announced by the School.</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.4372670807453416</v>
+        <v>0.4058376839107736</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ECE606</t>
+          <t>EARTH491</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Algorithm Design and Analysis</t>
+          <t>Special Topics in Earth and Environmental Sciences</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>This is an introductory course on algorithms at the graduate level. It assumes familiarity with basic data structures such as lists, queues, trees and graphs, and emphasizes creativity in the design of algorithms, and rigorous analysis. Correctness (soundness and completeness) and efficiency (with respect to average-, best- and worst-case time and space) properties are considered in the context of algorithms for classes of problems such as optimization and decision problems. The course also gives insights into when a problem may be intractable, and how we may deal with intractability.</t>
+          <t>A lecture course offered in a particular area of Earth and Environmental Sciences, subject to availablity of instructor.</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.6752383708953857</v>
+        <v>0.4027284339946509</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SEED642</t>
+          <t>ECE250</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stakeholder Engagement, Collaborations and Partnerships</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>This course builds competences in the development and deployment of strategies and processes (in for-and not-for-profit organizations) to engage both internal and external stakeholders in opportunities to accelerate sustainability.  Content covers: the identification, characterization and valuation of primary and secondary stakeholders; drivers and challenges; engagement approaches, including traditional and social media forms of communication, consultation, conflict resolution, and cross-sector partnerships.  Content also introduces: structures, including informal vs. formal interactions, face-to-face and distance meetings, industry associations, joint ventures, public-private partnerships, networks and business to not-for-profit collaborations; processes, such as partnership formation, decision-making, monitoring of progress; and strategic considerations, such as business value, risk management, control vs. influence, barriers and confluence points.  Students working as a team will present their recommendations on a real time case study to stakeholders involved.</t>
+          <t>Data structures, abstract data types, recursive algorithms, algorithm analysis, sorting and searching, and problem-solving strategies.</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.6567916870117188</v>
+        <v>0.4010980868508959</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Financial Planning</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ARTSDEAN653</t>
+          <t>GER211</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>International Organizations and Public Policy</t>
+          <t>Contemporary German Language and Culture</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>This course explores international organizations' contributions to transnational or "multilevel" governance and the instruments (both hard and soft) that they can wield.  Students assess the role of international organizations in transnational policy diffusion by focusing first on major international organizations such as the International Monetary Fund, the World Bank and the OECD and then examine key policy areas such as the environment, food and development.</t>
+          <t>This course develops reading, writing, and oral skills, and intercultural competence.</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.6408394575119019</v>
+        <v>0.3792070874861573</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ARCH685</t>
+          <t>HUMSC289</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Readings and Seminars in Architecture</t>
+          <t>Special Topics in Human Sciences</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Issues to be negotiated on an individual basis with faculty members. An outline of this course, approved by the professor in charge, must be submitted to the Graduate Officer within three weeks of registration.</t>
+          <t>An in-depth analysis of research in selected topics in the human sciences.</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.9733429902228465</v>
+        <v>0.3684622246620463</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>STATACTSC938</t>
+          <t>HUMSC389</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Statistical Consulting</t>
+          <t>Special Topics in Human Sciences</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>This course will cover some of the basic tools of a statistical consultant. Topics will include the use of statistical packages, problem-solving techniques, discussion of common statistical consulting problems, effective communication of statistical concepts and management of consulting sessions.</t>
+          <t>An in-depth analysis of research in selected topics in the human sciences.</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.855376898188422</v>
+        <v>0.3684622246620463</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ERS102</t>
+          <t>HUMSC489</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sustainability and the Really Long View</t>
+          <t>Special Topics in Human Sciences</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Focusing on the relationship between complexity and energy in bio-physical, ecological and social contexts, we review  trends in 'Big History' as it has unfolded from the Big Bang to the Internet. 
-The course explores the implications of this 'deep-time' perspective for our understanding of the great challenge of sustainability.</t>
+          <t>An in-depth analysis of research in selected topics in the human sciences.</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.8494650016494425</v>
+        <v>0.3684622246620463</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ARCH685</t>
+          <t>CS497</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Readings and Seminars in Architecture</t>
+          <t>Multidisciplinary Studies in Computer Science</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Issues to be negotiated on an individual basis with faculty members. An outline of this course, approved by the professor in charge, must be submitted to the Graduate Officer within three weeks of registration.</t>
+          <t>See the Course Offerings list for topics available.</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.9733428359031677</v>
+        <v>0.3684234663705813</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>STATACTSC938</t>
+          <t>CS146</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Statistical Consulting</t>
+          <t>Elementary Algorithm Design and Data Abstraction (Advanced Level)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>This course will cover some of the basic tools of a statistical consultant. Topics will include the use of statistical packages, problem-solving techniques, discussion of common statistical consulting problems, effective communication of statistical concepts and management of consulting sessions.</t>
+          <t>CS146 is an advanced-level version of CS136.</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8553768396377563</v>
+        <v>0.3680256506272234</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ERS102</t>
+          <t>PHYS449</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sustainability and the Really Long View</t>
+          <t>Machine Learning in Physics</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Focusing on the relationship between complexity and energy in bio-physical, ecological and social contexts, we review  trends in 'Big History' as it has unfolded from the Big Bang to the Internet. 
-The course explores the implications of this 'deep-time' perspective for our understanding of the great challenge of sustainability.</t>
+          <t>Machine learning applications in the physical sciences.</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.849465012550354</v>
+        <v>2.449489742783178</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PMATH950</t>
+          <t>ECE250</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Topics in Analysis</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Topics in Analysis</t>
+          <t>Data structures, abstract data types, recursive algorithms, algorithm analysis, sorting and searching, and problem-solving strategies.</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.6060060060060061</v>
+        <v>1.664100588675687</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ENGL790</t>
+          <t>GEOG484</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Discourse Analysis</t>
+          <t>Machine Learning in Geospatial Science</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Discourse Analysis</t>
+          <t>An in-depth study of current machine learning algorithms and their applications in geospatial science, with a focus on earth observation data processing and analysis. Topics include k-nearest neighbour, decision trees, support vector machines, ensemble learning, and some deep neural networks (e.g., CNN, U-Net). Machine learning algorithms implemented using Python will be applied for semantic segmentation, land use and land cover classification, and building and road detection using aerial and satellite images.</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.501871101871102</v>
+        <v>1.571428571428571</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PHYS773</t>
+          <t>MTE140</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Special Topics in Physics</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Special Topics in Physics</t>
+          <t>This course emphasizes the following topics: structured software design data structures, abstract data types, recursive algorithms, algorithm analysis and design, sorting and searching, hashing, and problem-solving strategies.</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.4730769230769231</v>
+        <v>1.309307341415954</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SEED404</t>
+          <t>SYDE223</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>International Development Theory</t>
+          <t>Data Structures and Algorithms</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>This course emphasizes both theoretical and conceptual frameworks, techniques, practices and methods for analysis of development, focusing in particular on the historical and spatial trajectory of international development through an examination of seminal texts.</t>
+          <t>Algorithms and data structures emphasizes the following topics: structured software design, data structures, abstract data types, recursive algorithms, algorithm analysis and design, sorting and searching, hashing, problem-solving strategies and NP-completeness.</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.7166472673416138</v>
+        <v>1.309307341415954</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>GEOG607</t>
+          <t>ECON424</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fundamentals of Geographic Information Systems</t>
+          <t>Machine Learning in Economics</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Introduces the fundamentals of GIS at a graduate level, including cartographic best practices, map projections and coordinate systems, georeferencing data, quantitative mapping, web mapping, and introductory spatial analysis, including clustering, network, and multicriteria analysis. Intended for students without significant experience in GIS. *eligible for MES.</t>
+          <t>This course is an introduction to prediction in economics using machine learning. Topics may include supervised and unsupervised learning, text analysis, regression trees, penalized regression, classification, random forest, neural network, and boosting methods.</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.5652446746826172</v>
+        <v>1.224744871391589</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Geospatial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>7</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GEOG187</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Geospatial Data Science</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>A specialized introduction to fundamental concepts and emerging trends in geomatics and geospatial data science. Overview of the geospatial industry, including application in government, research, and private sector. Students are introduced to cross-discipline tools and techniques for accessing, visualizing, and analyzing geospatial data.</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1.133893419027682</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PHIL458</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Studies in the Philosophy of Science</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Special topics in the philosophy of science, as announced by the department.</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1.133893419027682</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MSE240</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Algorithms and Data Structures</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Design and analysis of data structures and algorithms with an emphasis on further development of computer programming skills. Topics include algorithms for searching, sorting, stacks, queues, trees, and graphs. Comparison of algorithms on different data structures. Solutions to common engineering problems in computer science using algorithms and data structures. Introduction to mathematical analysis of space and time complexity with a focus on designing solutions that can scale to large input sizes.</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1.12089707663561</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AMATH445</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Scientific Machine Learning</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>The course provides an in-depth exploration of how deep learning techniques are applied in various scientific and medical domains. The course introduces basic concepts of deep learning, explores different deep learning architectures and algorithms, and focuses on their applications in scientific and biomedical research. The integration of scientific knowledge with machine learning techniques is emphasized throughout the course. Students will gain hands-on experience by executing the acquired concepts using Python.</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1.106797181058933</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>bert</t>
         </is>
       </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PHYS449</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Machine Learning in Physics</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Machine learning applications in the physical sciences.</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.5983653664588928</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CS480</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Introduction to Machine Learning</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Introduction to modelling and algorithmic techniques for machines to learn concepts from data. Generalization: underfitting, overfitting, cross-validation. Tasks: classification, regression, clustering. Optimization-based learning: loss minimization. regularization. Statistical learning: maximum likelihood, Bayesian learning. Algorithms: nearest neighbour, (generalized) linear regression, mixtures of Gaussians, Gaussian processes, kernel methods, support vector machines, deep learning, sequence learning, ensemble techniques. Large scale learning: distributed learning and stream learning. Applications: Natural language processing, computer vision, data mining, human computer interaction, information retrieval.</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.5959513783454895</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MSE546</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Advanced Machine Learning</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>This course provides a deeper understanding of machine learning (ML) techniques by utilizing students' prior background in ML and operations research to understand the drivers of ML methodologies rather than using black-box processes. The course first reviews supervised and unsupervised learning methods, and then dives deeper into their assumptions, mathematical models, and underlying algorithms to help students systematically develop and enhance ML processes. Using the same approach, the course covers more advanced topics in ML, such as neural networks and reinforcement learning. Application areas within this course may include, but are not limited to healthcare, energy, sports, transportation, and manufacturing.</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.5695852637290955</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>STAT441</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Statistical Learning - Classification</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Classification is the problem of predicting a discrete outcome from a set of explanatory variables. Main topics include logistic regression, neural networks, tree-based methods, support vector machines, and nearest neighbour methods. Other topics include model assessment, training, and tuning.</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.5467572212219238</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CS485</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Statistical and Computational Foundations of Machine Learning</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Extracting meaningful patterns from random samples of large data sets. Statistical analysis of the resulting problems. Common algorithmic paradigms for such tasks. Central concepts: VC-dimension, margins of a classifier, sparsity and description length, other types of regularization. Performance guarantees: generalization bounds, data dependent error bounds, and computational complexity of learning algorithms. Common paradigms: neural networks, kernel methods and support-vector machines, boosting, nearest neighbor classifiers. Applications to data mining.</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.5330299735069275</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AFM346</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Applications of Predictive Analytics in Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>This course introduces applications of classification/prediction methods and machine learning used in accounting and finance settings. Samples include bankruptcy prediction, fraud detection, and loan default.</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.5298211574554443</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ECON424</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Machine Learning in Economics</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>This course is an introduction to prediction in economics using machine learning. Topics may include supervised and unsupervised learning, text analysis, regression trees, penalized regression, classification, random forest, neural network, and boosting methods.</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.5236376523971558</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MSE446</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Introduction to Machine Learning</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>This course provides an introduction to machine learning, including supervised and unsupervised learning. Emphasis is placed on proper procedures for the training and testing of models. Topics covered may include data cleaning and transformation, overfitting and generalization, n-fold cross validation, regression, decision trees, neural networks, rule finding, and clustering. Students learn to apply machine learning methods to management engineering problems using common tools such as R and Python.</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.507680356502533</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SYDE522</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Foundations of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>The objective of this course is to introduce students to fundamental concepts of artificial intelligence. An overview of different learning schemes will be provided, including supervised and unsupervised algorithms. The focus of this course will be on dimensionality reduction, clustering, classification, deep and shallow artificial neural networks, and reinforcement learning. Ethical aspects of artificial intelligence will be discussed.</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.5018159151077271</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>10</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ECE406</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Algorithm Design and Analysis</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Design and analysis of efficient, correct algorithms. Advanced data structures, divide-and-conquer algorithms, recurrences, greedy algorithms, dynamic programming, graph algorithms, search and backtrack, inherently hard and unsolvable problems, approximation and randomized algorithms, and amortized analysis.</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.4976229071617126</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PHYS449</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Machine Learning in Physics</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Machine learning applications in the physical sciences.</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.9441407211956092</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GEOG484</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Machine Learning in Geospatial Science</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>An in-depth study of current machine learning algorithms and their applications in geospatial science, with a focus on earth observation data processing and analysis. Topics include k-nearest neighbour, decision trees, support vector machines, ensemble learning, and some deep neural networks (e.g., CNN, U-Net). Machine learning algorithms implemented using Python will be applied for semantic segmentation, land use and land cover classification, and building and road detection using aerial and satellite images.</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.7898517878036694</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ECE250</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Algorithms and Data Structures</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Data structures, abstract data types, recursive algorithms, algorithm analysis, sorting and searching, and problem-solving strategies.</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.7475287187553025</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CS485</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Statistical and Computational Foundations of Machine Learning</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Extracting meaningful patterns from random samples of large data sets. Statistical analysis of the resulting problems. Common algorithmic paradigms for such tasks. Central concepts: VC-dimension, margins of a classifier, sparsity and description length, other types of regularization. Performance guarantees: generalization bounds, data dependent error bounds, and computational complexity of learning algorithms. Common paradigms: neural networks, kernel methods and support-vector machines, boosting, nearest neighbor classifiers. Applications to data mining.</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.624060780697792</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CS480</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Introduction to Machine Learning</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Introduction to modelling and algorithmic techniques for machines to learn concepts from data. Generalization: underfitting, overfitting, cross-validation. Tasks: classification, regression, clustering. Optimization-based learning: loss minimization. regularization. Statistical learning: maximum likelihood, Bayesian learning. Algorithms: nearest neighbour, (generalized) linear regression, mixtures of Gaussians, Gaussian processes, kernel methods, support vector machines, deep learning, sequence learning, ensemble techniques. Large scale learning: distributed learning and stream learning. Applications: Natural language processing, computer vision, data mining, human computer interaction, information retrieval.</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.6173994938892637</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AMATH445</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Scientific Machine Learning</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>The course provides an in-depth exploration of how deep learning techniques are applied in various scientific and medical domains. The course introduces basic concepts of deep learning, explores different deep learning architectures and algorithms, and focuses on their applications in scientific and biomedical research. The integration of scientific knowledge with machine learning techniques is emphasized throughout the course. Students will gain hands-on experience by executing the acquired concepts using Python.</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.6055452614477662</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>MSE240</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Algorithms and Data Structures</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Design and analysis of data structures and algorithms with an emphasis on further development of computer programming skills. Topics include algorithms for searching, sorting, stacks, queues, trees, and graphs. Comparison of algorithms on different data structures. Solutions to common engineering problems in computer science using algorithms and data structures. Introduction to mathematical analysis of space and time complexity with a focus on designing solutions that can scale to large input sizes.</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.601976299153009</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ECON424</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Machine Learning in Economics</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>This course is an introduction to prediction in economics using machine learning. Topics may include supervised and unsupervised learning, text analysis, regression trees, penalized regression, classification, random forest, neural network, and boosting methods.</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.5984748728624221</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SYDE223</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Data Structures and Algorithms</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Algorithms and data structures emphasizes the following topics: structured software design, data structures, abstract data types, recursive algorithms, algorithm analysis and design, sorting and searching, hashing, problem-solving strategies and NP-completeness.</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0.598093976833912</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>machine learning algorithms and data science</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MSE446</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Introduction to Machine Learning</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>This course provides an introduction to machine learning, including supervised and unsupervised learning. Emphasis is placed on proper procedures for the training and testing of models. Topics covered may include data cleaning and transformation, overfitting and generalization, n-fold cross validation, regression, decision trees, neural networks, rule finding, and clustering. Students learn to apply machine learning methods to management engineering problems using common tools such as R and Python.</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0.5832345994647069</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>course_code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ECON206</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Money and Banking 1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>This course offers an overview of the functioning of the financial system both in Canada and abroad. It includes discussions of money and inflation, financial assets, and financial institutions and intermediaries.</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8752624556285491</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AFM422</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Management of Financial Institutions</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>This course focuses on the economics of financial institutions, particularly commercial banks. Issues related to commercial and investment banking and other financial intermediaries as well as financial markets and regulatory entities are examined.</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8631328672306871</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AFM322</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Derivative Securities</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>This course will further develop students' understanding and knowledge of an important area of financial markets by introducing derivatives, their financial applications, value, and how they can be used to manage financial risk. Derivatives discussed may include options, futures, forwards, and swaps. Students will learn how to utilize derivatives to manage financial risk.</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8541487391883342</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ACTSC291</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8399344949441387</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AFM272</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8399344949441387</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AFM373</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cases and Applications in Corporate Finance</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>This course builds on the theory of financial management using cases to illustrate a variety of corporate financial decisions.</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8372656915819131</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.835288590537687</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AFM273</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Financial Instruments and Capital Markets</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>This course is the second in a two-course sequence which offers an overview of global capital markets. The course focuses on valuation of financial instruments and the theories of financial risk and diversification.</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8111891033980306</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AFM276</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>This course introduces fundamental tools of analysis and valuation to prepare students to research, interpret, and analyze financial statements. The course examines financial reporting from the perspective of the financial statement user with an emphasis on interpretation of financial disclosures for cash flow analysis, risk assessment, forecasting, and decision making.</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8044159190201161</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CFM101</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Markets and Data Analytics</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>This course introduces financial markets and institutions, commonly used financial data, and data schema and visualization therein. It covers fundamental functions of financial institutions and their usage of data, and basic financial data management techniques. The course will focus on buy side institutions and stock market data.</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7724849783810567</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ECON206</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Money and Banking 1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>This course offers an overview of the functioning of the financial system both in Canada and abroad. It includes discussions of money and inflation, financial assets, and financial institutions and intermediaries.</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8752624988555908</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AFM422</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Management of Financial Institutions</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>This course focuses on the economics of financial institutions, particularly commercial banks. Issues related to commercial and investment banking and other financial intermediaries as well as financial markets and regulatory entities are examined.</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8631328940391541</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AFM322</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Derivative Securities</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>This course will further develop students' understanding and knowledge of an important area of financial markets by introducing derivatives, their financial applications, value, and how they can be used to manage financial risk. Derivatives discussed may include options, futures, forwards, and swaps. Students will learn how to utilize derivatives to manage financial risk.</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8541487455368042</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AFM272</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8399344086647034</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ACTSC291</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8399344086647034</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AFM373</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cases and Applications in Corporate Finance</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>This course builds on the theory of financial management using cases to illustrate a variety of corporate financial decisions.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.83726567029953</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8352887034416199</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AFM273</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Financial Instruments and Capital Markets</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>This course is the second in a two-course sequence which offers an overview of global capital markets. The course focuses on valuation of financial instruments and the theories of financial risk and diversification.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8111891746520996</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AFM276</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>This course introduces fundamental tools of analysis and valuation to prepare students to research, interpret, and analyze financial statements. The course examines financial reporting from the perspective of the financial statement user with an emphasis on interpretation of financial disclosures for cash flow analysis, risk assessment, forecasting, and decision making.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8044158816337585</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CFM101</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Markets and Data Analytics</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>This course introduces financial markets and institutions, commonly used financial data, and data schema and visualization therein. It covers fundamental functions of financial institutions and their usage of data, and basic financial data management techniques. The course will focus on buy side institutions and stock market data.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7724850177764893</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ECON206</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Money and Banking 1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>This course offers an overview of the functioning of the financial system both in Canada and abroad. It includes discussions of money and inflation, financial assets, and financial institutions and intermediaries.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8752624556285491</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AFM373</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Cases and Applications in Corporate Finance</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>This course builds on the theory of financial management using cases to illustrate a variety of corporate financial decisions.</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.8372656915819131</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AFM322</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Derivative Securities</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>This course will further develop students' understanding and knowledge of an important area of financial markets by introducing derivatives, their financial applications, value, and how they can be used to manage financial risk. Derivatives discussed may include options, futures, forwards, and swaps. Students will learn how to utilize derivatives to manage financial risk.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8541487391883342</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AFM422</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Management of Financial Institutions</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>This course focuses on the economics of financial institutions, particularly commercial banks. Issues related to commercial and investment banking and other financial intermediaries as well as financial markets and regulatory entities are examined.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8631328672306871</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ACTSC291</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8399344949441387</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CFM101</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Markets and Data Analytics</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>This course introduces financial markets and institutions, commonly used financial data, and data schema and visualization therein. It covers fundamental functions of financial institutions and their usage of data, and basic financial data management techniques. The course will focus on buy side institutions and stock market data.</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7724849783810567</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>COMM421</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>This advanced course in financial statement analysis provides a framework for using financial statement data in a variety of business analysis and valuation contexts.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7622662795493094</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.835288590537687</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AFM276</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>This course introduces fundamental tools of analysis and valuation to prepare students to research, interpret, and analyze financial statements. The course examines financial reporting from the perspective of the financial statement user with an emphasis on interpretation of financial disclosures for cash flow analysis, risk assessment, forecasting, and decision making.</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.8044159190201161</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AFM273</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Financial Instruments and Capital Markets</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>This course is the second in a two-course sequence which offers an overview of global capital markets. The course focuses on valuation of financial instruments and the theories of financial risk and diversification.</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.8111891033980306</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ACTSC291</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.002607041270297566</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0.002570912292821616</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AFM272</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.002544152327929449</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AFM273</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Financial Instruments and Capital Markets</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>This course is the second in a two-course sequence which offers an overview of global capital markets. The course focuses on valuation of financial instruments and the theories of financial risk and diversification.</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.002501814031419181</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AFM276</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>This course introduces fundamental tools of analysis and valuation to prepare students to research, interpret, and analyze financial statements. The course examines financial reporting from the perspective of the financial statement user with an emphasis on interpretation of financial disclosures for cash flow analysis, risk assessment, forecasting, and decision making.</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.002501814031419181</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AFM322</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Derivative Securities</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>This course will further develop students' understanding and knowledge of an important area of financial markets by introducing derivatives, their financial applications, value, and how they can be used to manage financial risk. Derivatives discussed may include options, futures, forwards, and swaps. Students will learn how to utilize derivatives to manage financial risk.</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.002493864780925356</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AFM373</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cases and Applications in Corporate Finance</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>This course builds on the theory of financial management using cases to illustrate a variety of corporate financial decisions.</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.002487975822722363</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AFM422</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Management of Financial Institutions</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>This course focuses on the economics of financial institutions, particularly commercial banks. Issues related to commercial and investment banking and other financial intermediaries as well as financial markets and regulatory entities are examined.</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.002416193516555728</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CFM101</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Markets and Data Analytics</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>This course introduces financial markets and institutions, commonly used financial data, and data schema and visualization therein. It covers fundamental functions of financial institutions and their usage of data, and basic financial data management techniques. The course will focus on buy side institutions and stock market data.</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.002396019029359339</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ECON206</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Money and Banking 1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>This course offers an overview of the functioning of the financial system both in Canada and abroad. It includes discussions of money and inflation, financial assets, and financial institutions and intermediaries.</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.002300910094307773</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>COMM421</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>This advanced course in financial statement analysis provides a framework for using financial statement data in a variety of business analysis and valuation contexts.</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.4287480362950998</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ARCH520</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Special Topics in Urbanism and Landscape</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>A range of special topics courses within urbanism and landscape.</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3947690989670001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CHEM323</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Analytical Instrumentation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Detailed study of selected instruments and instrumental methods. Introduction to chemometrics and to computer interfacing.</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.3695971359714633</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CHEM224L</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Analytical Instrumentation Laboratory</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Extensive lab experience for students who have taken CHEM220.</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.3651826986572749</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>THPERF490</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Selected Seminars in Drama &amp; Theatre Arts</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Seminars in special areas of drama and theatre.</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0.364924578527063</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>THPERF491</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Selected Seminars in Drama &amp; Theatre Arts</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Seminars in special areas of drama and theatre.</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.364924578527063</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AFM212</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Financial Analysis and Planning</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>This course develops an in-depth understanding of financial statements as a system for analysis and planning as a foundation for upper-year accounting and finance courses.</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.3633059246666435</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PHIL265</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>The Existentialist Experience</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>An introduction to existentialism using both literary and philosophical texts.</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.3527506014434643</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AFM391</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Intermediate Financial Accounting 2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>This is an intermediate financial accounting course that deals with problems related to the measurement of liabilities, measurement of income, and the reporting and measuring of corporate equities.</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3497986338689935</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0.3468768905021173</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1.109400392450458</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>COMM421</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>This advanced course in financial statement analysis provides a framework for using financial statement data in a variety of business analysis and valuation contexts.</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1.109400392450458</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AFM212</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Financial Analysis and Planning</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>This course develops an in-depth understanding of financial statements as a system for analysis and planning as a foundation for upper-year accounting and finance courses.</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1.032795558988644</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AFM276</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>This course introduces fundamental tools of analysis and valuation to prepare students to research, interpret, and analyze financial statements. The course examines financial reporting from the perspective of the financial statement user with an emphasis on interpretation of financial disclosures for cash flow analysis, risk assessment, forecasting, and decision making.</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0.9284766908852594</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AFM491</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Advanced Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>An advanced accounting course considering specific problems of accounting for the corporate entity, such as business combinations, intercorporate investments, consolidated financial statements, accounting for foreign operations and foreign currency transactions, and segment reporting.</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8528028654224417</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AFM391</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Intermediate Financial Accounting 2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>This is an intermediate financial accounting course that deals with problems related to the measurement of liabilities, measurement of income, and the reporting and measuring of corporate equities.</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8017837257372732</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
       <c r="C58" t="n">
+        <v>7</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AFM273</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Financial Instruments and Capital Markets</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>This course is the second in a two-course sequence which offers an overview of global capital markets. The course focuses on valuation of financial instruments and the theories of financial risk and diversification.</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.7276068751089989</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>COMM101</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Markets</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>The course introduces students to the role of finance in the global economy and aims to develop students' understanding of the basic principles of financial decision-making.</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0.7276068751089989</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CFM401</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Topics in Financial Technology</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>This course introduces current topics in financial technology. Students will apply data analytics or general computational concepts to gain a better understanding of new financial technology.</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AFM291</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Intermediate Financial Accounting 1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>A first course in intermediate accounting dealing with the theory and practice of financial statement preparation and reporting. The emphasis will be on asset valuation and the related impact on income measurement.</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0.6882472016116852</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>COMM421</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>This advanced course in financial statement analysis provides a framework for using financial statement data in a variety of business analysis and valuation contexts.</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.5720502138137817</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AFM212</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Financial Analysis and Planning</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>This course develops an in-depth understanding of financial statements as a system for analysis and planning as a foundation for upper-year accounting and finance courses.</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.5658434629440308</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
         <v>3</v>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>GBDA206</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Introduction to Business Financials</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>In this course students will be exposed to a variety of techniques to interpret financial statements. Students will analyze balance sheets, income, and cash flow statements and will engage in the formulation of a comprehensive business plan.</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.547735333442688</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AFM276</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>This course introduces fundamental tools of analysis and valuation to prepare students to research, interpret, and analyze financial statements. The course examines financial reporting from the perspective of the financial statement user with an emphasis on interpretation of financial disclosures for cash flow analysis, risk assessment, forecasting, and decision making.</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.5394580364227295</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.513144850730896</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AFM323</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Quantitative Foundations for Finance</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>This course introduces analytical and statistical methods commonly used in finance, with applications to investment management and corporate finance.</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.479210376739502</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>STAT374</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Quantitative Foundations for Finance</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>This course introduces analytical and statistical methods commonly used in finance, with applications to investment management and corporate finance.</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.479210376739502</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MGMT171</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Fundamentals of Personal and Business Finance</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Review of the concept and applications of the time value of money. Overview of common consumer and small business oriented financial products with a focus on the Canadian economy. Introduction to the use of spreadsheets and apps that aid in understanding and comparing financial scenarios.</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.4445341825485229</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CFM401</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Topics in Financial Technology</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>This course introduces current topics in financial technology. Students will apply data analytics or general computational concepts to gain a better understanding of new financial technology.</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.4383511245250702</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>10</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ECON206</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Money and Banking 1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>This course offers an overview of the functioning of the financial system both in Canada and abroad. It includes discussions of money and inflation, financial assets, and financial institutions and intermediaries.</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.4295753836631775</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AFM101</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Accounting</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>This course is an introduction to financial accounting. The preparation and use of financial statements is examined. The accounting cycle and assets and liabilities reporting, is discussed.</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.7279998855325558</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>COMM421</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>This advanced course in financial statement analysis provides a framework for using financial statement data in a variety of business analysis and valuation contexts.</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.7269462639169691</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AFM276</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Financial Statement Analysis</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>This course introduces fundamental tools of analysis and valuation to prepare students to research, interpret, and analyze financial statements. The course examines financial reporting from the perspective of the financial statement user with an emphasis on interpretation of financial disclosures for cash flow analysis, risk assessment, forecasting, and decision making.</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.6796436841107129</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AFM391</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Intermediate Financial Accounting 2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>This is an intermediate financial accounting course that deals with problems related to the measurement of liabilities, measurement of income, and the reporting and measuring of corporate equities.</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.610109199302722</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AFM422</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Management of Financial Institutions</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>This course focuses on the economics of financial institutions, particularly commercial banks. Issues related to commercial and investment banking and other financial intermediaries as well as financial markets and regulatory entities are examined.</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.6028197440889727</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AFM212</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Financial Analysis and Planning</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>This course develops an in-depth understanding of financial statements as a system for analysis and planning as a foundation for upper-year accounting and finance courses.</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.6009022270779009</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AFM273</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Financial Instruments and Capital Markets</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>This course is the second in a two-course sequence which offers an overview of global capital markets. The course focuses on valuation of financial instruments and the theories of financial risk and diversification.</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.5709551003650368</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AFM373</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cases and Applications in Corporate Finance</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>This course builds on the theory of financial management using cases to illustrate a variety of corporate financial decisions.</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.5541018717640498</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ACTSC291</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Global Capital Markets and Financial Analytics</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>This course offers an overview of global capital markets and asset valuation. Topics may include an overview of financial markets and instruments, time value of money, valuation of financial assets, and financial risk and portfolio management. The course utilizes an analytic and computational approach to the topics, enabling students to develop data management and analysis competencies.</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0.5504903724640592</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>analyze financial statements using Python and Excel</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CFM401</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Topics in Financial Technology</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>This course introduces current topics in financial technology. Students will apply data analytics or general computational concepts to gain a better understanding of new financial technology.</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0.5503133187391807</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>course_code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CLAS260</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7203845585379419</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SCI266</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7203845585379419</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PHIL260</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7203845585379419</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RCS101</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7147614514621538</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GRK101</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7147614514621538</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RCS102</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7086807147314309</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GRK102</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7086807147314309</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SCI238</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Introductory Astronomy</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>A survey course in astronomy. The solar system, the Sun and planets, stars, the Milky Way, galaxies, and cosmology.</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.683629588050671</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CLAS123</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Classical Studies in Pop Culture</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>An introduction to the role that classical studies and the classical cultures have played in pop culture. This course will examine specific references, such as ancient Greek myths, and more general trends, such as literary types, in contemporary movies, television shows, comic books, and video games to illustrate the continued fascination with the cultures of Ancient Greece and Rome.</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6482310096202712</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SRF317</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>History of Sexuality: The Pre-Modern Period</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>This course introduces students to the history of Western sexuality, beginning with the ancient world and focusing primarily on the Middle Ages and the transition to modernity.</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.647333326067129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SCI266</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7203845381736755</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PHIL260</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7203845381736755</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CLAS260</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7203845381736755</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RCS101</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.71476149559021</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GRK101</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.71476149559021</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RCS102</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7086808085441589</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GRK102</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7086808085441589</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SCI238</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Introductory Astronomy</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>A survey course in astronomy. The solar system, the Sun and planets, stars, the Milky Way, galaxies, and cosmology.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6836296319961548</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CLAS123</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Classical Studies in Pop Culture</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>An introduction to the role that classical studies and the classical cultures have played in pop culture. This course will examine specific references, such as ancient Greek myths, and more general trends, such as literary types, in contemporary movies, television shows, comic books, and video games to illustrate the continued fascination with the cultures of Ancient Greece and Rome.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.648231029510498</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>faiss</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HIST317</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>History of Sexuality: The Pre-Modern Period</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>This course introduces students to the history of Western sexuality, beginning with the ancient world and focusing primarily on the Middle Ages and the transition to modernity.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6473333239555359</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CLAS260</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7203845585379419</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HIST317</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>History of Sexuality: The Pre-Modern Period</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>This course introduces students to the history of Western sexuality, beginning with the ancient world and focusing primarily on the Middle Ages and the transition to modernity.</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.647333326067129</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GRK102</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.7086807147314309</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SCI238</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Introductory Astronomy</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>A survey course in astronomy. The solar system, the Sun and planets, stars, the Milky Way, galaxies, and cosmology.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.683629588050671</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CLAS361</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>History of Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>In this course students will examine one or more important figures, periods, or issues in ancient philosophy. Plato and Aristotle are among the philosophers who may be covered.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.6018852773687389</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CLAS251</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Greek History</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>A survey of ancient Greek history, from the Bronze Age to Alexander the Great, emphasizing particularly its political and military aspects.</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6240635200405502</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CLAS123</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Classical Studies in Pop Culture</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>An introduction to the role that classical studies and the classical cultures have played in pop culture. This course will examine specific references, such as ancient Greek myths, and more general trends, such as literary types, in contemporary movies, television shows, comic books, and video games to illustrate the continued fascination with the cultures of Ancient Greece and Rome.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6482310096202712</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JS215</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Visions of Israel in Judaism: From Biblical to Modern Times</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>This course surveys the significance of the land of Israel in Judaism from historical, textual, and religious perspectives. Topics covered include the politics of Ancient Israel; the concept of Israel in prayer and the rabbinic and medieval Jewish imagination; portrayals of Israel in Christian and Muslim texts; and the origins, visions, and challenges of Zionism and the modern State of Israel.</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.547761386271666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CLAS237</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>The Ancient Near East and Egypt</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>A study of the civilizations of the ancient Near East focusing on Mesopotamia (Sumer and Akkad, the Babylonian Dynasty, and the Third Dynasty of Ur), Hatti, Assyria, Egypt, and Persia.</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5723848012123446</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mmr</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>GRK101</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.7147614514621538</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CLAS123</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Classical Studies in Pop Culture</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>An introduction to the role that classical studies and the classical cultures have played in pop culture. This course will examine specific references, such as ancient Greek myths, and more general trends, such as literary types, in contemporary movies, television shows, comic books, and video games to illustrate the continued fascination with the cultures of Ancient Greece and Rome.</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0010505746518251</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CLAS260</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0010505746518251</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GRK101</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0010505746518251</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GRK102</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.001042374179329811</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HIST317</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>History of Sexuality: The Pre-Modern Period</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>This course introduces students to the history of Western sexuality, beginning with the ancient world and focusing primarily on the Middle Ages and the transition to modernity.</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.001042374179329811</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PHIL260</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.001033506321464166</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RCS101</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.001033506321464166</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RCS102</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0009969729472010093</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SCI238</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Introductory Astronomy</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>A survey course in astronomy. The solar system, the Sun and planets, stars, the Milky Way, galaxies, and cosmology.</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0009453493403803728</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SCI266</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ancient Science</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>The ancient Greeks developed scientific theories that were influential for over a thousand years. Their worldview was different from ours, but they sought to explain some of the same phenomena that we grapple with today. In this course, we will study ancient Greek theories and methodologies in the sciences, which may include physics, astronomy, mathematics, meteorology, cosmology, astrology, and geography.</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0009440402012891553</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CO499</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Reading in Combinatorics and Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Reading course as announced by the department.</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3887261904761904</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EARTH491</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Special Topics in Earth and Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>A lecture course offered in a particular area of Earth and Environmental Sciences, subject to availablity of instructor.</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3642009826833237</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SI375R</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Special Topics in Islamic and Arab Cultures</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>This course allows for in-depth study of selected topics in Islam, Islamic cultures, or Arab cultures.</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.3571951322334954</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CLAS261</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Great Works: Ancient and Medieval</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>A historical survey of ancient and medieval philosophy in the Western tradition.</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.3553255419379911</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PHIL283</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Great Works: Ancient and Medieval</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>A historical survey of ancient and medieval philosophy in the Western tradition.</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0.3553255419379911</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PACS290</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Special Topics in Peace and Conflict Studies</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>A seminar course exploring special issues related to peace and conflict. Content will vary from year to year.</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.3512776867145799</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>GER495</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Reading Course in Approved Topics</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Reading course in topics chosen in consultation with an advisor.</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.346024961252957</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CLAS461</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Studies in Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Special topics in ancient philosophy, as announced by the department.</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.3428503787878788</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PHIL403</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Studies in Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Special topics in ancient philosophy, as announced by the department.</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3428503787878788</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fuzzy_multi</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AFM212</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Financial Analysis and Planning</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>This course develops an in-depth understanding of financial statements as a system for analysis and planning as a foundation for upper-year accounting and finance courses.</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0.3400668896321071</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AMATH495</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Reading Course</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Reading course as announced by the department.</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CLAS461</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Studies in Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Special topics in ancient philosophy, as announced by the department.</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1.133893419027682</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GER495</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Reading Course in Approved Topics</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Reading course in topics chosen in consultation with an advisor.</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1.133893419027682</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PHIL403</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Studies in Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Special topics in ancient philosophy, as announced by the department.</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1.133893419027682</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AVIA426</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Professional Pilot Program Course 6</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>This course continues from AVIA325 and completes the Professional Pilot Program Course.</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1.060660171779821</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CLAS237</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>The Ancient Near East and Egypt</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>A study of the civilizations of the ancient Near East focusing on Mesopotamia (Sumer and Akkad, the Babylonian Dynasty, and the Third Dynasty of Ur), Hatti, Assyria, Egypt, and Persia.</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>7</v>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HIST315</t>
+          <t>CLAS261</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>U.S. and the World</t>
+          <t>Great Works: Ancient and Medieval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>This course examines the history of foreign relations of the United States from the "Age of Imperialism" through the "War on Terror". Topics will include the Great War, Wilsonianism, World War 2, the Cold War, human rights, and post-9/11 U.S. foreign policies.</t>
+          <t>A historical survey of ancient and medieval philosophy in the Western tradition.</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.5642697811126709</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HIST237</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>The Ancient Near East and Egypt</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>A study of the civilizations of the ancient Near East focusing on Mesopotamia (Sumer and Akkad, the Babylonian Dynasty, and the Third Dynasty of Ur), Hatti, Assyria, Egypt, and Persia.</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PHIL283</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Great Works: Ancient and Medieval</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>A historical survey of ancient and medieval philosophy in the Western tradition.</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>keyword_overlap</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CLAS361</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>History of Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>In this course students will examine one or more important figures, periods, or issues in ancient philosophy. Plato and Aristotle are among the philosophers who may be covered.</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0.8728715609439696</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ANTH204</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Biological Anthropology</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>This course surveys the lines of inquiry in biological anthropology including evolutionary theory, anthropological genetics, primatology, hominin fossil record, osteology and skeletal biology, and modern human biocultural adaptations. A laboratory component provides students an experiential approach to the material.</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.5572061538696289</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ANTH292</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Skeletons: Sex, Disease, and Death</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>This course will provide a general introduction to how human remains have been used to reconstruct perspectives on life and death in ancient societies. Topics will include sex, gender and sexuality, cannibalism, human sacrifice, body modification, disease, and beliefs about the supernatural, among others.</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.5559298396110535</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BIOL360</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Evolution 2: Fossil Record</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>An overview of the origin of life, how it evolved and diversified, modern principles of paleontology with particular emphasis on analytical tools to interpret ancient life forms. Patterns, processes of evolution, and paleoecology of key groups of microfossils, invertebrates, plants, vertebrates, and their trace fossils.</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.5382494926452637</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EARTH336</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Evolution 2: Fossil Record</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>An overview of the origin of life, how it evolved and diversified, modern principles of paleontology with particular emphasis on analytical tools to interpret ancient life forms. Patterns, processes of evolution, and paleoecology of key groups of microfossils, invertebrates, plants, vertebrates, and their trace fossils.</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.5382494926452637</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ANTH455</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Skeletal Biology and Forensics</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>This laboratory course focuses on the evaluation of human skeletal remains in archaeological and forensic contexts. Topics include determination of basic biological categories (e.g., age, sex, race), evaluation of paleopathological conditions, and aspects of forensic anthropology.</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.5213471055030823</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MEDVL492</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Medieval Archaeology Field School</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>This course offers learners an intensive introduction to archaeological methods and interpretation through fieldwork. It focuses on a live excavation. Learners will also, to a more limited extent, experience field lectures and discussions, hands-on training, laboratory work, and visits to archaeological sites and museums. Learning sessions will include topics such as the history and archaeology, stratigraphy, general principles of artifact conservation, identification of the main classes of artifacts and procedures to follow in the archaeology lab, use of survey tools and software, heritage protection, and appropriate display of finds.</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.5173106789588928</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ANTH355</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Human Osteology</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>A laboratory course in the anatomy and function of the human skeleton with an emphasis on recovering and identifying skeletal remains from archaeological and forensic contexts.</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.515101432800293</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HIST112</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Science and Technology in Global History</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>This course introduces students to the history of science and technology in a global perspective from the ancient period through the twenty-first century, with an emphasis on the creation and exchange of major ideas, developments, and practices across cultures and continents. Students will examine the social and cultural role of science and technology, reading and interpreting historical documents to study the development of universal knowledge and how societies define progress using scientific reasoning and technological change. Students will be expected to develop their writing and critical thinking skills through a series of written assignments throughout the term.</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.4984172284603119</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ANTH322</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>The Archaeology of the Great Lakes Area</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>An in-depth study of the archaeological evidence for prehistoric cultures in the Great Lakes area from their arrival ca. 11,000 years ago to the coming of Europeans. Cultural ecology and cultural evolution will be stressed.</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.4983893632888794</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bert</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>10</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ANTH305</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Paleopathology of Health and Disease</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>This course introduces students to the identification and interpretation of skeletal evidence for disease, ancient and modern concepts of health and disease, and current clinical interpretations of skeletal pathologies. Topics include pathology in archaeological remains and the process of developing a differential diagnosis of skeletal lesions.</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.4963907599449158</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CLAS361</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>History of Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>In this course students will examine one or more important figures, periods, or issues in ancient philosophy. Plato and Aristotle are among the philosophers who may be covered.</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.5648154639843461</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PHIL380</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>History of Ancient Philosophy</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>In this course students will examine one or more important figures, periods, or issues in ancient philosophy. Plato and Aristotle are among the philosophers who may be covered.</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.5648154639843461</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CLAS261</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Great Works: Ancient and Medieval</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>A historical survey of ancient and medieval philosophy in the Western tradition.</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.5643398275141893</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PHIL283</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Great Works: Ancient and Medieval</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>A historical survey of ancient and medieval philosophy in the Western tradition.</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.5643398275141893</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RCS101</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.5602394881239027</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GRK101</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>This course is designed for students beginning the study of ancient Greek. It covers the foundational grammar of Attic and Hellenistic Greek and is the first step in preparing students to read original ancient Greek texts for the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.5596241035085181</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CLAS237</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>The Ancient Near East and Egypt</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>A study of the civilizations of the ancient Near East focusing on Mesopotamia (Sumer and Akkad, the Babylonian Dynasty, and the Third Dynasty of Ur), Hatti, Assyria, Egypt, and Persia.</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.5561727618971176</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>HIST237</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>The Ancient Near East and Egypt</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>A study of the civilizations of the ancient Near East focusing on Mesopotamia (Sumer and Akkad, the Babylonian Dynasty, and the Third Dynasty of Ur), Hatti, Assyria, Egypt, and Persia.</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.5561727618971176</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>RCS102</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0.5387041335975032</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>a course about dinosaurs, fossils and ancient civilizations</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hybrid_ensemble</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GRK102</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Introductory Ancient Greek 2</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>This course is a continuation of GRK101/RCS101. The majority of the rules of ancient Greek grammar will be covered by the end of the course. Students will begin to read more complex ancient Greek texts relevant to the study of classical studies and religious studies.</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0.5380887489821186</v>
       </c>
     </row>
   </sheetData>
